--- a/05-material-de-apoyo/05-normalizacion.xlsx
+++ b/05-material-de-apoyo/05-normalizacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git-projects\FFdBBdDD\05-material-de-apoyo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A12C45C-8C7E-4776-A9DF-992A9BCECCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B929776F-3198-4100-97AC-053D78D53BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{8DD5B17A-0B7F-4EB5-AA42-EA0DD621BEEE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{8DD5B17A-0B7F-4EB5-AA42-EA0DD621BEEE}"/>
   </bookViews>
   <sheets>
     <sheet name="1FN" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>AlumnoID</t>
   </si>
@@ -307,6 +307,15 @@
   </si>
   <si>
     <t>Identificado</t>
+  </si>
+  <si>
+    <t>(Mejora: separar nombre y apellidos)</t>
+  </si>
+  <si>
+    <t>(dependencias funcionales)</t>
+  </si>
+  <si>
+    <t>(Acá llegamos a la 3FN ya que separamos nombre de profesor de la tabla curso)</t>
   </si>
 </sst>
 </file>
@@ -330,12 +339,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -350,13 +365,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,13 +382,13 @@
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -387,6 +403,64 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>467710</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>120869</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4361793</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>99848</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D74D70-4F35-A878-D28D-A402D543BE1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="467710" y="5454869"/>
+          <a:ext cx="7089228" cy="714703"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CA32814F-C2CC-453D-865B-58036D6E226F}" name="Table2" displayName="Table2" ref="A1:I7" totalsRowShown="0">
   <autoFilter ref="A1:I7" xr:uid="{CA32814F-C2CC-453D-865B-58036D6E226F}"/>
@@ -399,7 +473,7 @@
     <tableColumn id="6" xr3:uid="{7B5F5B47-EADD-4425-8849-8FD7AD27658B}" name="ProfesoresIDs"/>
     <tableColumn id="7" xr3:uid="{3169C31D-C46B-4945-89A4-75CCDAE6A3AE}" name="ProfesoresNombres"/>
     <tableColumn id="8" xr3:uid="{6854342E-296C-4AA6-8FA9-629CB4527035}" name="FechasInscripcion"/>
-    <tableColumn id="9" xr3:uid="{BB95F515-E50E-42DD-B43A-DEF5A21B862A}" name="NotasFinales" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{BB95F515-E50E-42DD-B43A-DEF5A21B862A}" name="NotasFinales" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -416,7 +490,7 @@
     <tableColumn id="5" xr3:uid="{698FAA20-F4B4-49CB-8A4E-2CE99D8881CF}" name="CursoNombre"/>
     <tableColumn id="6" xr3:uid="{E8EFB039-C0CC-4D01-92C8-15F165BD86A3}" name="ProfesorID"/>
     <tableColumn id="7" xr3:uid="{F580B1F1-1CC2-48E7-B42C-7B2FCD13A142}" name="ProfesorNombre"/>
-    <tableColumn id="8" xr3:uid="{9B2FB150-F769-49E4-9639-141F9C81ACC3}" name="FechaInscripcion" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{9B2FB150-F769-49E4-9639-141F9C81ACC3}" name="FechaInscripcion" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{DF7DDAD3-6DBB-4555-B06F-B5A18A53EA8F}" name="NotaFinal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -447,7 +521,7 @@
     <tableColumn id="5" xr3:uid="{1DBEB035-7DA9-4F75-BDC1-17D662704B3B}" name="CursoNombre"/>
     <tableColumn id="6" xr3:uid="{64F6FCB5-BC6E-47A1-B7B1-2188FA566991}" name="ProfesorID"/>
     <tableColumn id="7" xr3:uid="{F2BCEA94-2348-4568-931E-E0967608C0BF}" name="ProfesorNombre"/>
-    <tableColumn id="8" xr3:uid="{E3CF5E8C-DA00-4CA2-8CE2-B5352399C1BF}" name="FechaInscripcion" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{E3CF5E8C-DA00-4CA2-8CE2-B5352399C1BF}" name="FechaInscripcion" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{380A73DE-0A78-4380-ADB9-AA35FDD82F19}" name="NotaFinal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -495,7 +569,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{5744E11F-4A1C-454D-9D69-968A18D523F2}" name="AlumnoID"/>
     <tableColumn id="2" xr3:uid="{8F144BA6-33D6-4AD1-B28F-3E1DDE4D16FB}" name="CursoID"/>
-    <tableColumn id="3" xr3:uid="{63BCC68F-12D6-4B97-BFD4-1C638BF53982}" name="FechaInscripcion" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{63BCC68F-12D6-4B97-BFD4-1C638BF53982}" name="FechaInscripcion" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{372F0AAE-725F-44A4-9C8A-9E50023A05EC}" name="NotaFinal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1076,6 +1150,9 @@
       <c r="D11" t="s">
         <v>56</v>
       </c>
+      <c r="G11" s="4" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1456,7 +1533,7 @@
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
@@ -1796,6 +1873,9 @@
       <c r="D13" t="s">
         <v>88</v>
       </c>
+      <c r="F13" s="4" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1839,12 +1919,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1855,7 +1935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1866,7 +1946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1877,7 +1957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1888,7 +1968,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1899,7 +1979,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -1910,7 +1990,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1921,12 +2001,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -1934,23 +2014,29 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
       <c r="B30" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1958,7 +2044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -2187,13 +2273,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="6">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>